--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 MOUNTAIN GOAT HUNTER CHOICE O.I.L.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 MOUNTAIN GOAT HUNTER CHOICE O.I.L.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$19</definedName>
@@ -711,7 +711,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -780,7 +784,11 @@
           <t>88.9</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -849,7 +857,11 @@
           <t>89.5</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>6.3</t>
@@ -918,7 +930,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
           <t>7.0</t>
@@ -987,7 +1003,11 @@
           <t>80.0</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -1056,7 +1076,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -1125,7 +1149,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t>6.0</t>
@@ -1194,7 +1222,11 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>7.7</t>
@@ -1263,7 +1295,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1332,7 +1368,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -1401,7 +1441,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>11.5</t>
@@ -1470,7 +1514,11 @@
           <t>91.7</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -1539,7 +1587,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -1608,7 +1660,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -1677,7 +1733,11 @@
           <t>90.0</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -1746,7 +1806,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
           <t>2.7</t>
